--- a/artfynd/A 45590-2024 artfynd.xlsx
+++ b/artfynd/A 45590-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122745387</v>
       </c>
       <c r="B2" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122745386</v>
       </c>
       <c r="B3" t="n">
-        <v>91628</v>
+        <v>91632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 45590-2024 artfynd.xlsx
+++ b/artfynd/A 45590-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745387</v>
+        <v>122745386</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>91632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595769</v>
+        <v>595760</v>
       </c>
       <c r="R2" t="n">
-        <v>7083175</v>
+        <v>7083169</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745386</v>
+        <v>122745387</v>
       </c>
       <c r="B3" t="n">
-        <v>91632</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595760</v>
+        <v>595769</v>
       </c>
       <c r="R3" t="n">
-        <v>7083169</v>
+        <v>7083175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 45590-2024 artfynd.xlsx
+++ b/artfynd/A 45590-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745386</v>
+        <v>122745387</v>
       </c>
       <c r="B2" t="n">
-        <v>91632</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595760</v>
+        <v>595769</v>
       </c>
       <c r="R2" t="n">
-        <v>7083169</v>
+        <v>7083175</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745387</v>
+        <v>122745386</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>91632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595769</v>
+        <v>595760</v>
       </c>
       <c r="R3" t="n">
-        <v>7083175</v>
+        <v>7083169</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 45590-2024 artfynd.xlsx
+++ b/artfynd/A 45590-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122745387</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122745386</v>
       </c>
       <c r="B3" t="n">
-        <v>91632</v>
+        <v>91640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 45590-2024 artfynd.xlsx
+++ b/artfynd/A 45590-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122745387</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester, Helene Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -784,7 +784,7 @@
         <v>122745386</v>
       </c>
       <c r="B3" t="n">
-        <v>91640</v>
+        <v>91643</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester, Helene Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 45590-2024 artfynd.xlsx
+++ b/artfynd/A 45590-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122745387</v>
       </c>
       <c r="B2" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122745386</v>
       </c>
       <c r="B3" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
